--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY187"/>
+  <dimension ref="A1:AZ187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137876</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137877</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220816</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220819</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220820</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220821</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56220824</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718058</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1798,6 +1848,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718900</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1916,6 +1971,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392590</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2034,6 +2094,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392900</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2152,6 +2217,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392958</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2268,6 +2338,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555399</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2384,6 +2459,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60899366</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2500,6 +2580,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60899367</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2616,6 +2701,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69340636</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2732,6 +2822,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62077764</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2842,6 +2937,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392520</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2958,6 +3058,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555404</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3074,6 +3179,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555405</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3171,6 +3281,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/233033</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3287,6 +3402,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442409</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3394,6 +3514,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442629</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3510,6 +3635,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442654</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3617,6 +3747,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442681</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3724,6 +3859,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442790</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3831,6 +3971,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442863</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3938,6 +4083,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442882</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4045,6 +4195,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442955</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4155,6 +4310,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718669</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4265,6 +4425,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718850</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4383,6 +4548,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392552</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4501,6 +4671,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392557</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4598,6 +4773,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/268944</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4714,6 +4894,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555437</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4830,6 +5015,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53820285</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4948,6 +5138,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392585</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5071,6 +5266,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392632</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5188,6 +5388,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555452</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5320,6 +5525,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555462</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5426,6 +5636,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75968029</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5542,6 +5757,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555482</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5652,6 +5872,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718843</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5768,6 +5993,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69340632</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5865,6 +6095,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/373883</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5981,6 +6216,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59944261</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6097,6 +6337,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59944262</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6213,6 +6458,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555498</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6329,6 +6579,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555417</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6426,6 +6681,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/548014</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6542,6 +6802,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60791697</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6658,6 +6923,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60791700</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6774,6 +7044,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60791701</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6890,6 +7165,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60791703</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7006,6 +7286,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60791704</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7122,6 +7407,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60791705</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7240,6 +7530,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718759</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7355,6 +7650,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392616</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7473,6 +7773,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392847</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7570,6 +7875,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/595003</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7667,6 +7977,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/866423</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7774,6 +8089,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555400</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7884,6 +8204,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67717985</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7994,6 +8319,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392254</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8095,6 +8425,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75968008</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8192,6 +8527,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1075345</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8308,6 +8648,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56381117</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8409,6 +8754,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967875</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8524,6 +8874,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392924</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8634,6 +8989,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75968027</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8735,6 +9095,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75968036</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8851,6 +9216,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555401</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8967,6 +9337,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555402</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9068,6 +9443,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967865</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9184,6 +9564,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555406</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9300,6 +9685,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555407</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9416,6 +9806,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555409</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9532,6 +9927,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555410</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9648,6 +10048,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555414</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9764,6 +10169,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555415</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9880,6 +10290,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555416</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9990,6 +10405,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67719482</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10100,6 +10520,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392572</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10210,6 +10635,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392930</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10326,6 +10756,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555420</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10436,6 +10871,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718110</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10546,6 +10986,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392440</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10662,6 +11107,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555425</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10778,6 +11228,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555427</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10894,6 +11349,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555428</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11010,6 +11470,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555429</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11126,6 +11591,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555430</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11242,6 +11712,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555431</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11352,6 +11827,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718028</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11462,6 +11942,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392896</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11578,6 +12063,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555432</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11694,6 +12184,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555434</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11810,6 +12305,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555435</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11926,6 +12426,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555436</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12036,6 +12541,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67717347</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12152,6 +12662,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555438</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12268,6 +12783,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555439</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12384,6 +12904,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555441</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12500,6 +13025,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555442</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12601,6 +13131,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967859</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12717,6 +13252,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555443</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12833,6 +13373,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555444</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12949,6 +13494,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555445</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13067,6 +13617,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392750</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13185,6 +13740,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392893</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13295,6 +13855,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67719759</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13405,6 +13970,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392741</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13515,6 +14085,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67717469</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13625,6 +14200,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392638</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13741,6 +14321,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75891338</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13857,6 +14442,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555448</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13973,6 +14563,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555450</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14083,6 +14678,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73445944</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14193,6 +14793,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67717341</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14294,6 +14899,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967818</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14410,6 +15020,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555451</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14528,6 +15143,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392836</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14644,6 +15264,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555471</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14760,6 +15385,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555472</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14861,6 +15491,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967856</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14962,6 +15597,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967863</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15078,6 +15718,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555483</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15194,6 +15839,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555485</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15310,6 +15960,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555486</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15417,6 +16072,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555489</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15533,6 +16193,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555491</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15649,6 +16314,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555492</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15765,6 +16435,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555494</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15881,6 +16556,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555495</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15991,6 +16671,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392729</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16092,6 +16777,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967871</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16193,6 +16883,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967989</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16303,6 +16998,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67717334</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16413,6 +17113,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392537</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16514,6 +17219,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967819</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16615,6 +17325,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967881</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16737,6 +17452,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555393</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16834,6 +17554,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2937313</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16941,6 +17666,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62554960</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17053,6 +17783,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392809</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17150,6 +17885,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2316834</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17257,6 +17997,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62554961</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17364,6 +18109,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62554962</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17476,6 +18226,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392574</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17573,6 +18328,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4051198</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17689,6 +18449,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555390</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17801,6 +18566,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392783</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17903,6 +18673,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75972478</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18006,6 +18781,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257922</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18103,6 +18883,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6419160</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18209,6 +18994,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67717419</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18306,6 +19096,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6588197</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18422,6 +19217,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164590</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18538,6 +19338,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164591</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18654,6 +19459,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164640</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18770,6 +19580,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164642</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18886,6 +19701,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164643</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19002,6 +19822,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164673</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19118,6 +19943,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164674</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19236,6 +20066,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164675</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19351,6 +20186,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67717310</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19466,6 +20306,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718664</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19584,6 +20429,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67718687</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19685,6 +20535,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967882</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19807,6 +20662,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555481</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19908,6 +20768,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967873</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20009,6 +20874,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967984</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20110,6 +20980,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967855</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20207,6 +21082,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6611599</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20323,6 +21203,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555464</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20439,6 +21324,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555465</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20555,6 +21445,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555468</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20671,6 +21566,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69340633</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20781,6 +21681,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392268</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20882,6 +21787,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75967988</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20998,6 +21908,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555473</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21105,6 +22020,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555475</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21221,6 +22141,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62555476</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21338,6 +22263,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69340634</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21453,8 +22383,201 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73392435</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91420</v>
+        <v>91557</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91559</v>
+        <v>91561</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91561</v>
+        <v>91562</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91562</v>
+        <v>91563</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91564</v>
+        <v>91570</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91571</v>
+        <v>91577</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91577</v>
+        <v>91584</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91584</v>
+        <v>91585</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>

--- a/artfynd/S 1944-2026 artfynd.xlsx
+++ b/artfynd/S 1944-2026 artfynd.xlsx
@@ -21456,7 +21456,7 @@
         <v>69340633</v>
       </c>
       <c r="B180" t="n">
-        <v>91585</v>
+        <v>91598</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
